--- a/internal_doc/05.测试设计/参数校验/测试用例/集群管理（sdb管理）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/集群管理（sdb管理）参数校验测试用例.xlsx
@@ -86,14 +86,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bin/sdbcmd，有效参数测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdbcmd，无效参数测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sequoiadb/bin/sdbcmd
 Command options:
   -h [ --help ]       help
@@ -113,14 +105,6 @@
     <t>1、sdbadmin用户进入sequoiadb/bin目录，执行sdbcmd脚本参数错误，如：
   执行./sdbcmd -a
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdbcmtop，有效参数测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdbcmtop，无效参数测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -184,14 +168,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bin/sdblist，--version查看版本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdblist，-h [ --help ]查看帮助</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>参数：-t [ --type ] arg     node type: db/om/cm/all, default: db</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -221,38 +197,6 @@
   </si>
   <si>
     <t>参数：--expand              show expanded details</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdblist，-t [ --type ]指定节点类型查看节点信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdblist，-p [ --svcname ]指定端口查看节点信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdblist，-m [ --mode ]指定mode类型查看节点信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdblist，-r [ --role ]指定角色类型查看节点信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdblist，-l [ --long ]查看节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdblist，--detail查看节点详情</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdblist，--expand查看节点扩展信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdblist，不带参数执行</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -364,14 +308,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bin/sdblist，参数错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bin/sdblist，-p指定的端口错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、sdbadmin用户进入sequoiadb/bin目录，执行sdblist查看节点信息，-p指定的端口错误，覆盖如下场景：
   a.端口不存在
   b.端口非db/cm/om端口
@@ -394,6 +330,54 @@
   <si>
     <t>执行报错，执行结果返回所有参数的参数说明</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bin/sdblist，-h [ --help ]查看帮助_st.verify.CMConf.046</t>
+  </si>
+  <si>
+    <t>bin/sdblist，--version查看版本_st.verify.CMConf.047</t>
+  </si>
+  <si>
+    <t>bin/sdblist，-t [ --type ]指定节点类型查看节点信息_st.verify.CMConf.048</t>
+  </si>
+  <si>
+    <t>bin/sdblist，-p [ --svcname ]指定端口查看节点信息_st.verify.CMConf.049</t>
+  </si>
+  <si>
+    <t>bin/sdblist，-p指定的端口错误_st.verify.CMConf.050</t>
+  </si>
+  <si>
+    <t>bin/sdblist，-m [ --mode ]指定mode类型查看节点信息_st.verify.CMConf.051</t>
+  </si>
+  <si>
+    <t>bin/sdblist，-r [ --role ]指定角色类型查看节点信息_st.verify.CMConf.052</t>
+  </si>
+  <si>
+    <t>bin/sdblist，-l [ --long ]查看节点_st.verify.CMConf.053</t>
+  </si>
+  <si>
+    <t>bin/sdblist，--detail查看节点详情_st.verify.CMConf.054</t>
+  </si>
+  <si>
+    <t>bin/sdblist，--expand查看节点扩展信息_st.verify.CMConf.055</t>
+  </si>
+  <si>
+    <t>bin/sdblist，不带参数执行_st.verify.CMConf.056</t>
+  </si>
+  <si>
+    <t>bin/sdblist，参数错误_st.verify.CMConf.057</t>
+  </si>
+  <si>
+    <t>bin/sdbcmd，有效参数测试_st.verify.CMConf.058</t>
+  </si>
+  <si>
+    <t>bin/sdbcmd，无效参数测试_st.verify.CMConf.059</t>
+  </si>
+  <si>
+    <t>bin/sdbcmtop，有效参数测试_st.verify.CMConf.060</t>
+  </si>
+  <si>
+    <t>bin/sdbcmtop，无效参数测试_st.verify.CMConf.061</t>
   </si>
 </sst>
 </file>
@@ -496,13 +480,13 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
@@ -558,34 +542,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I18" tableType="xml" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" connectionId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I18" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
   <autoFilter ref="A1:I18"/>
   <tableColumns count="9">
-    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="10">
+    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="9">
+    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="7">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/summary" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="8">
+    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="6">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/preconditions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="7">
+    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="5">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/execution_type" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="6">
+    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="4">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/importance" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="5">
+    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="3">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/step_number" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="4">
+    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="2">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/actions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="3">
+    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="1">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/expectedresults" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" uniqueName="execution_type" name="execution_type2" dataDxfId="2">
+    <tableColumn id="9" uniqueName="execution_type" name="execution_type2" dataDxfId="0">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/execution_type" xmlDataType="integer"/>
     </tableColumn>
   </tableColumns>
@@ -888,8 +872,7 @@
     <col min="7" max="7" width="44.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="34" style="1" customWidth="1"/>
     <col min="9" max="9" width="6.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1">
@@ -952,13 +935,13 @@
     </row>
     <row r="3" spans="1:9" ht="67.5">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -966,19 +949,25 @@
       <c r="E3" s="1">
         <v>1</v>
       </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="81">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
@@ -986,88 +975,141 @@
       <c r="D4" s="4">
         <v>1</v>
       </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
       <c r="G4" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>56</v>
+        <v>42</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="108">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
       <c r="G5" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="189">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>62</v>
+        <v>48</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="94.5">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
       <c r="G7" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="81">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
       <c r="G8" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>64</v>
+        <v>50</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="135">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
@@ -1075,19 +1117,28 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
       <c r="G9" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="148.5">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -1095,111 +1146,164 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
       <c r="G10" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="108">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="108">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
       <c r="G12" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="54">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
       <c r="G13" s="2" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="54">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
       <c r="G14" s="1" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>73</v>
+        <v>57</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="148.5">
       <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="4">
-        <v>2</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I15" s="4">
+        <v>25</v>
+      </c>
+      <c r="I15" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="94.5">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>18</v>
@@ -1207,22 +1311,28 @@
       <c r="D16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
       <c r="G16" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="148.5">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>18</v>
@@ -1230,25 +1340,25 @@
       <c r="D17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="4">
-        <v>2</v>
-      </c>
-      <c r="F17" s="4">
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="4">
+      <c r="I17" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="94.5">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
@@ -1256,15 +1366,21 @@
       <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
       <c r="G18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="4"/>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
